--- a/Excel/StasticalFunctions1.xlsx
+++ b/Excel/StasticalFunctions1.xlsx
@@ -8,20 +8,28 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01_AF\ANP-D6211\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8380CB9E-FCEA-44CF-85BE-4ABBC24F3A7B}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277734B4-BDF4-4ABC-82DF-ADDD199E509C}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="1" xr2:uid="{D4213206-02E2-40C9-BF57-AE4CDB31715B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="7680" windowHeight="10930" activeTab="3" xr2:uid="{D4213206-02E2-40C9-BF57-AE4CDB31715B}"/>
   </bookViews>
   <sheets>
     <sheet name="SUM|SUMIF|SUMIFS" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="COUNT|COUNTIF|COUNTIFS" sheetId="2" r:id="rId2"/>
+    <sheet name="AVERAGE|AVERAGEIF|AVERAGEIFS" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="City3">'AVERAGE|AVERAGEIF|AVERAGEIFS'!$A$2:$A$11</definedName>
+    <definedName name="City4">Sheet4!$A$2:$A$11</definedName>
     <definedName name="Division1">'SUM|SUMIF|SUMIFS'!$C$2:$C$11</definedName>
     <definedName name="DOJ1_">'SUM|SUMIF|SUMIFS'!$B$2:$B$11</definedName>
-    <definedName name="Fruits1">Sheet2!$A$2:$A$11</definedName>
+    <definedName name="Fruits1">'COUNT|COUNTIF|COUNTIFS'!$A$2:$A$11</definedName>
+    <definedName name="Fruits3">'AVERAGE|AVERAGEIF|AVERAGEIFS'!$B$2:$B$11</definedName>
+    <definedName name="Fruits4">Sheet4!$B$2:$B$11</definedName>
     <definedName name="Name1">'SUM|SUMIF|SUMIFS'!$A$2:$A$11</definedName>
-    <definedName name="Quantity1">Sheet2!$B$2:$B$11</definedName>
+    <definedName name="Quantity1">'COUNT|COUNTIF|COUNTIFS'!$B$2:$B$11</definedName>
+    <definedName name="Quantity3">'AVERAGE|AVERAGEIF|AVERAGEIFS'!$C$2:$C$11</definedName>
+    <definedName name="Quantity4">Sheet4!$C$2:$C$11</definedName>
     <definedName name="Salary1">'SUM|SUMIF|SUMIFS'!$D$2:$D$11</definedName>
   </definedNames>
   <calcPr calcId="179021"/>
@@ -34,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="72">
   <si>
     <t>Name1</t>
   </si>
@@ -133,6 +141,123 @@
   </si>
   <si>
     <t>Count the quantity between 60 and 80</t>
+  </si>
+  <si>
+    <t>City3</t>
+  </si>
+  <si>
+    <t>Fruits3</t>
+  </si>
+  <si>
+    <t>Quantity3</t>
+  </si>
+  <si>
+    <t>Raigad</t>
+  </si>
+  <si>
+    <t>Ratnagiri</t>
+  </si>
+  <si>
+    <t>Goa</t>
+  </si>
+  <si>
+    <t>Sangli</t>
+  </si>
+  <si>
+    <t>Satara</t>
+  </si>
+  <si>
+    <t>Thane</t>
+  </si>
+  <si>
+    <t>Wardha</t>
+  </si>
+  <si>
+    <t>Washim</t>
+  </si>
+  <si>
+    <t>Jack Fruit</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>Lemon</t>
+  </si>
+  <si>
+    <t>What is the Average means.?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formula of th avg =&gt; </t>
+  </si>
+  <si>
+    <t>Average of Quantity</t>
+  </si>
+  <si>
+    <t>Average Quantity of Banana</t>
+  </si>
+  <si>
+    <t>average of Quantity &gt; 60</t>
+  </si>
+  <si>
+    <t>Average Quantity of Apples and Banana</t>
+  </si>
+  <si>
+    <t>Average of Apples in Goa</t>
+  </si>
+  <si>
+    <t>Sum of Total Values / Total Number of Values</t>
+  </si>
+  <si>
+    <t>City4</t>
+  </si>
+  <si>
+    <t>Fruits4</t>
+  </si>
+  <si>
+    <t>Quantity4</t>
+  </si>
+  <si>
+    <t>FruitName</t>
+  </si>
+  <si>
+    <t>CityName</t>
+  </si>
+  <si>
+    <t>minimum Quantity</t>
+  </si>
+  <si>
+    <t>Maximum Quantity</t>
+  </si>
+  <si>
+    <t>Minimun Quantity for the mentioned Fruit</t>
+  </si>
+  <si>
+    <t>Maximum Quantity of the Mentioned Fruit</t>
+  </si>
+  <si>
+    <t>minimum Quantity of the mentioned fruit in the mentioned city</t>
+  </si>
+  <si>
+    <t>maximum Quantity of the mentioned fruit in the mentioned city</t>
+  </si>
+  <si>
+    <t>Smallest Quantity</t>
+  </si>
+  <si>
+    <t>2nd Smallest Quantity</t>
+  </si>
+  <si>
+    <t>5th Smallest Quantity</t>
+  </si>
+  <si>
+    <t>Largest Value of the Quantity</t>
+  </si>
+  <si>
+    <t>2nd Highest Quantity</t>
+  </si>
+  <si>
+    <t>5th Highest Quantity</t>
   </si>
 </sst>
 </file>
@@ -142,7 +267,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -193,8 +318,21 @@
       <name val="Segoe UI"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -218,8 +356,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -242,6 +392,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -250,7 +413,7 @@
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -278,6 +441,9 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -291,6 +457,21 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Accent5" xfId="2" builtinId="45"/>
@@ -704,7 +885,7 @@
       <c r="D6" s="5">
         <v>17000</v>
       </c>
-      <c r="F6" s="11" t="s">
+      <c r="F6" s="12" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="7">
@@ -741,7 +922,7 @@
       <c r="D8" s="5">
         <v>50000</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G8" s="7">
@@ -776,7 +957,7 @@
       <c r="D10" s="5">
         <v>19000</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="F10" s="12" t="s">
         <v>21</v>
       </c>
       <c r="G10" s="7">
@@ -799,7 +980,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="F12" s="12" t="s">
+      <c r="F12" s="13" t="s">
         <v>22</v>
       </c>
       <c r="G12" s="9">
@@ -826,10 +1007,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="17.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>24</v>
       </c>
     </row>
@@ -837,7 +1018,7 @@
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="15">
         <v>99</v>
       </c>
     </row>
@@ -845,10 +1026,10 @@
       <c r="A3" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="15">
         <v>80</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="17" t="s">
         <v>29</v>
       </c>
       <c r="E3" s="9">
@@ -864,7 +1045,7 @@
       <c r="A4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="15">
         <v>76</v>
       </c>
     </row>
@@ -872,10 +1053,10 @@
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="15">
         <v>76</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="17" t="s">
         <v>30</v>
       </c>
       <c r="E5" s="7">
@@ -891,7 +1072,7 @@
       <c r="A6" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B6" s="15">
+      <c r="B6" s="16">
         <v>68</v>
       </c>
     </row>
@@ -899,10 +1080,10 @@
       <c r="A7" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="15">
+      <c r="B7" s="16">
         <v>49</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="17" t="s">
         <v>31</v>
       </c>
       <c r="E7" s="9">
@@ -914,7 +1095,7 @@
       <c r="A8" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="15">
         <v>48</v>
       </c>
     </row>
@@ -922,10 +1103,10 @@
       <c r="A9" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="15">
+      <c r="B9" s="16">
         <v>80</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="17" t="s">
         <v>32</v>
       </c>
       <c r="E9" s="7">
@@ -937,7 +1118,7 @@
       <c r="A10" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="15">
+      <c r="B10" s="16">
         <v>99</v>
       </c>
     </row>
@@ -945,7 +1126,7 @@
       <c r="A11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="15">
         <v>15</v>
       </c>
     </row>
@@ -953,4 +1134,575 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B4B45B8-3502-448D-98DD-85580E0F8A6C}">
+  <dimension ref="A1:I15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13.26953125" customWidth="1"/>
+    <col min="2" max="2" width="15.1796875" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="5" max="5" width="34.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="39.08984375" style="11" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="19">
+        <v>40</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="19">
+        <v>50</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>48</v>
+      </c>
+      <c r="F5" s="9" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" s="18">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C7" s="19">
+        <v>68</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="9">
+        <f>AVERAGE(Quantity3)</f>
+        <v>57.7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="18">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="18">
+        <v>76</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F9" s="9">
+        <f>AVERAGEIF(Fruits3,"Banana",Quantity3)</f>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C10" s="18">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C11" s="18">
+        <v>99</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="9">
+        <f>AVERAGEIF(Quantity3,"&gt;=60",Quantity3)</f>
+        <v>79.8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E13" s="21" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="9" t="e">
+        <f>AVERAGEIFS(Quantity3,Fruits3,"Banana",Fruits3,"Apple")</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="G13" s="9">
+        <f>(AVERAGEIF(Fruits3,"Banana",Quantity3) + AVERAGEIF(Fruits3,"Apples",Quantity3))/2</f>
+        <v>58</v>
+      </c>
+      <c r="H13" s="9">
+        <f>AVERAGE(SUMIF(Fruits3,"Banana",Quantity3),SUMIF(Fruits3,"Apples",Quantity3))</f>
+        <v>58</v>
+      </c>
+      <c r="I13" s="9">
+        <f>(SUMIF(Fruits3,"Banana",Quantity3)+SUMIF(Fruits3,"Apples",Quantity3))/2</f>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="E15" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="9">
+        <f>AVERAGEIFS(Quantity3,City3,"Goa",Fruits3,"Apples")</f>
+        <v>40</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6ABD3C6-A2F9-4B9B-BAF2-85B71EFDB91C}">
+  <dimension ref="A1:I75"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.6328125" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.453125" customWidth="1"/>
+    <col min="6" max="6" width="13.08984375" customWidth="1"/>
+    <col min="8" max="8" width="57.7265625" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="11"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="17.5" x14ac:dyDescent="0.35">
+      <c r="A1" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2" s="19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" s="19">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="19">
+        <v>50</v>
+      </c>
+      <c r="E4" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="23" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="18">
+        <v>55</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="I5" s="9">
+        <f>MIN(Quantity4)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="19">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="18">
+        <v>73</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="9">
+        <f>MAX(Quantity4)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="18">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C9" s="18">
+        <v>80</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="I9" s="9">
+        <f>_xlfn.MINIFS(Quantity4,Fruits4,E5)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C10" s="18">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="17.5" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" s="18">
+        <v>150</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="I11" s="9">
+        <f>_xlfn.MAXIFS(Quantity4,Fruits4,E5)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H13" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="I13" s="9">
+        <f>_xlfn.MINIFS(Quantity4,Fruits4,E5,City4,F5)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="H15" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="I15" s="9">
+        <f>_xlfn.MAXIFS(Quantity4,Fruits4,E5,City4,F5)</f>
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D17" s="9">
+        <f>SMALL(Quantity4,1)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D18" s="9">
+        <f>SMALL(Quantity4,2)</f>
+        <v>40</v>
+      </c>
+      <c r="H18" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="9">
+        <f>SMALL(Quantity4,1)</f>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D19" s="9">
+        <f>SMALL(Quantity4,3)</f>
+        <v>50</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>67</v>
+      </c>
+      <c r="I19" s="9">
+        <f>SMALL(Quantity4,2)</f>
+        <v>40</v>
+      </c>
+    </row>
+    <row r="20" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D20" s="9">
+        <f>SMALL(Quantity4,4)</f>
+        <v>55</v>
+      </c>
+      <c r="H20" s="25" t="s">
+        <v>68</v>
+      </c>
+      <c r="I20" s="9">
+        <f>SMALL(Quantity4,5)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="21" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D21" s="9">
+        <f>SMALL(Quantity4,5)</f>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="22" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D22" s="9">
+        <f>SMALL(Quantity4,6)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="23" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D23" s="9">
+        <f>SMALL(Quantity4,7)</f>
+        <v>76</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="I23" s="9">
+        <f>LARGE(Quantity4,1)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="24" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D24" s="9">
+        <f>SMALL(Quantity4,8)</f>
+        <v>80</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="I24" s="9">
+        <f>LARGE(Quantity4,2)</f>
+        <v>99</v>
+      </c>
+    </row>
+    <row r="25" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D25" s="9">
+        <f>SMALL(Quantity4,9)</f>
+        <v>99</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="I25" s="9">
+        <f>LARGE(Quantity4,5)</f>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="4:9" x14ac:dyDescent="0.35">
+      <c r="D26" s="9">
+        <f>SMALL(Quantity4,10)</f>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B68" s="22" t="s">
+        <v>36</v>
+      </c>
+      <c r="C68" s="22" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B69" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C69" s="22" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B70" s="22" t="s">
+        <v>38</v>
+      </c>
+      <c r="C70" s="22" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B71" s="22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C71" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B72" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C72" s="22" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B73" s="22" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B74" s="22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C74" s="22"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.35">
+      <c r="B75" s="22" t="s">
+        <v>45</v>
+      </c>
+      <c r="C75" s="22"/>
+    </row>
+  </sheetData>
+  <sortState ref="A2:C11">
+    <sortCondition ref="C1"/>
+  </sortState>
+  <dataValidations disablePrompts="1" count="2">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E5" xr:uid="{3AE07EDD-E333-46B2-9FFC-7A008213B995}">
+      <formula1>$C$68:$C$73</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{92D22D22-F186-45DD-98EF-6BDD1E088828}">
+      <formula1>$B$68:$B$75</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>